--- a/Excel Practice @ Day 01.xlsx
+++ b/Excel Practice @ Day 01.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Codegnan\Data Analytics\Microsoft Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DA26 excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EDD6B2-0724-4318-9899-D620E8A3924E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EB0E7F-79CA-41A3-AB86-47524270FC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5FB56502-8CCC-4FEF-933B-4B92691D64CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{5FB56502-8CCC-4FEF-933B-4B92691D64CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -454,7 +454,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yy"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0"/>
@@ -591,7 +591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -615,7 +615,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -676,7 +675,9 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{E2204142-5304-4A2C-9D1D-F3F7ABF101EC}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1007,9 +1008,11 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="12.21875" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" ht="43.2">
+    <row r="2" spans="1:14" ht="28.8">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1027,56 +1030,74 @@
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
         <v>40000</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="13">
         <v>2</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15"/>
+      <c r="D3" s="13">
+        <f>B3*C3</f>
+        <v>80000</v>
+      </c>
+      <c r="E3" s="14">
+        <f>(D3/$D$6)*100</f>
+        <v>83.333333333333343</v>
+      </c>
       <c r="K3" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="13">
         <v>2000</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="13">
         <v>5</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="15"/>
+      <c r="D4" s="13">
+        <f>B4*C4</f>
+        <v>10000</v>
+      </c>
+      <c r="E4" s="14">
+        <f>(D4/$D$6)*100</f>
+        <v>10.416666666666668</v>
+      </c>
       <c r="J4" s="12"/>
-      <c r="K4" s="16">
+      <c r="K4" s="15">
         <v>0.4</v>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="15">
         <v>1.2</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="15">
         <v>0.12</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="13">
         <v>2000</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <v>3</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="15"/>
+      <c r="D5" s="13">
+        <f>B5*C5</f>
+        <v>6000</v>
+      </c>
+      <c r="E5" s="14">
+        <f>(D5/$D$6)*100</f>
+        <v>6.25</v>
+      </c>
       <c r="J5" s="12" t="s">
         <v>2</v>
       </c>
@@ -1091,6 +1112,10 @@
       </c>
     </row>
     <row r="6" spans="1:14">
+      <c r="D6">
+        <f>D3+D4+D5</f>
+        <v>96000</v>
+      </c>
       <c r="J6" t="s">
         <v>125</v>
       </c>
@@ -1145,16 +1170,19 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="13">
         <v>50000</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="16">
         <v>0.1</v>
       </c>
-      <c r="D9" s="14"/>
+      <c r="D9" s="13">
+        <f>B9*$C$9</f>
+        <v>5000</v>
+      </c>
       <c r="J9" t="s">
         <v>128</v>
       </c>
@@ -1169,14 +1197,17 @@
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="13">
         <v>1000</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="14"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="13">
+        <f>B10*$C$9</f>
+        <v>100</v>
+      </c>
       <c r="J10" t="s">
         <v>129</v>
       </c>
@@ -1191,14 +1222,17 @@
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>2000</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="14"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="13">
+        <f>B11*$C$9</f>
+        <v>200</v>
+      </c>
       <c r="J11" t="s">
         <v>130</v>
       </c>
@@ -1213,7 +1247,7 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="B13" s="18"/>
+      <c r="B13" s="17"/>
     </row>
     <row r="14" spans="1:14">
       <c r="J14" s="12" t="s">
@@ -1243,194 +1277,278 @@
       <c r="J16" t="s">
         <v>125</v>
       </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="13"/>
+      <c r="K16" s="15">
+        <f t="shared" ref="K16:M21" si="0">$K6*K$4</f>
+        <v>145.6</v>
+      </c>
+      <c r="L16" s="15">
+        <f t="shared" si="0"/>
+        <v>436.8</v>
+      </c>
+      <c r="M16" s="15">
+        <f t="shared" si="0"/>
+        <v>43.68</v>
+      </c>
+      <c r="N16" s="15">
+        <f t="shared" ref="N16:N21" si="1">K16+L16+M16</f>
+        <v>626.07999999999993</v>
+      </c>
     </row>
     <row r="17" spans="1:14">
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="17">
         <v>2</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="17">
         <v>3</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <v>4</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <v>5</v>
       </c>
       <c r="J17" t="s">
         <v>126</v>
       </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="13"/>
+      <c r="K17" s="15">
+        <f t="shared" si="0"/>
+        <v>154.80000000000001</v>
+      </c>
+      <c r="L17" s="15">
+        <f t="shared" si="0"/>
+        <v>464.4</v>
+      </c>
+      <c r="M17" s="15">
+        <f t="shared" si="0"/>
+        <v>46.44</v>
+      </c>
+      <c r="N17" s="15">
+        <f t="shared" si="1"/>
+        <v>665.6400000000001</v>
+      </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="19">
+      <c r="A18" s="18">
         <v>1</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="17">
         <f>$A18*B$17</f>
         <v>1</v>
       </c>
-      <c r="C18" s="18">
-        <f t="shared" ref="C18:F22" si="0">$A18*C$17</f>
+      <c r="C18" s="17">
+        <f t="shared" ref="C18:F22" si="2">$A18*C$17</f>
         <v>2</v>
       </c>
-      <c r="D18" s="18">
-        <f t="shared" si="0"/>
+      <c r="D18" s="17">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="E18" s="18">
-        <f t="shared" si="0"/>
+      <c r="E18" s="17">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="F18" s="18">
-        <f t="shared" si="0"/>
+      <c r="F18" s="17">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="J18" t="s">
         <v>127</v>
       </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="13"/>
+      <c r="K18" s="15">
+        <f t="shared" si="0"/>
+        <v>116</v>
+      </c>
+      <c r="L18" s="15">
+        <f t="shared" si="0"/>
+        <v>348</v>
+      </c>
+      <c r="M18" s="15">
+        <f t="shared" si="0"/>
+        <v>34.799999999999997</v>
+      </c>
+      <c r="N18" s="15">
+        <f t="shared" si="1"/>
+        <v>498.8</v>
+      </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="19">
+      <c r="A19" s="18">
         <v>2</v>
       </c>
-      <c r="B19" s="18">
-        <f t="shared" ref="B19:B22" si="1">$A19*B$17</f>
+      <c r="B19" s="17">
+        <f>$A19*B$17</f>
         <v>2</v>
       </c>
-      <c r="C19" s="18">
-        <f t="shared" si="0"/>
+      <c r="C19" s="17">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D19" s="18">
-        <f t="shared" si="0"/>
+      <c r="D19" s="17">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="E19" s="18">
-        <f t="shared" si="0"/>
+      <c r="E19" s="17">
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="F19" s="18">
-        <f t="shared" si="0"/>
+      <c r="F19" s="17">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="J19" t="s">
         <v>128</v>
       </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="13"/>
+      <c r="K19" s="15">
+        <f t="shared" si="0"/>
+        <v>136</v>
+      </c>
+      <c r="L19" s="15">
+        <f t="shared" si="0"/>
+        <v>408</v>
+      </c>
+      <c r="M19" s="15">
+        <f t="shared" si="0"/>
+        <v>40.799999999999997</v>
+      </c>
+      <c r="N19" s="15">
+        <f t="shared" si="1"/>
+        <v>584.79999999999995</v>
+      </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="19">
+      <c r="A20" s="18">
         <v>3</v>
       </c>
-      <c r="B20" s="18">
-        <f t="shared" si="1"/>
+      <c r="B20" s="17">
+        <f>$A20*B$17</f>
         <v>3</v>
       </c>
-      <c r="C20" s="18">
-        <f t="shared" si="0"/>
+      <c r="C20" s="17">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D20" s="18">
-        <f t="shared" si="0"/>
+      <c r="D20" s="17">
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="E20" s="18">
-        <f t="shared" si="0"/>
+      <c r="E20" s="17">
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="F20" s="18">
-        <f t="shared" si="0"/>
+      <c r="F20" s="17">
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="J20" t="s">
         <v>129</v>
       </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="13"/>
+      <c r="K20" s="15">
+        <f t="shared" si="0"/>
+        <v>104.4</v>
+      </c>
+      <c r="L20" s="15">
+        <f t="shared" si="0"/>
+        <v>313.2</v>
+      </c>
+      <c r="M20" s="15">
+        <f t="shared" si="0"/>
+        <v>31.32</v>
+      </c>
+      <c r="N20" s="15">
+        <f t="shared" si="1"/>
+        <v>448.92</v>
+      </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="19">
+      <c r="A21" s="18">
         <v>4</v>
       </c>
-      <c r="B21" s="18">
-        <f t="shared" si="1"/>
+      <c r="B21" s="17">
+        <f>$A21*B$17</f>
         <v>4</v>
       </c>
-      <c r="C21" s="18">
-        <f t="shared" si="0"/>
+      <c r="C21" s="17">
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="D21" s="18">
-        <f t="shared" si="0"/>
+      <c r="D21" s="17">
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="E21" s="18">
-        <f t="shared" si="0"/>
+      <c r="E21" s="17">
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="F21" s="18">
-        <f t="shared" si="0"/>
+      <c r="F21" s="17">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="J21" t="s">
         <v>130</v>
       </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="13"/>
+      <c r="K21" s="15">
+        <f t="shared" si="0"/>
+        <v>146</v>
+      </c>
+      <c r="L21" s="15">
+        <f t="shared" si="0"/>
+        <v>438</v>
+      </c>
+      <c r="M21" s="15">
+        <f t="shared" si="0"/>
+        <v>43.8</v>
+      </c>
+      <c r="N21" s="15">
+        <f t="shared" si="1"/>
+        <v>627.79999999999995</v>
+      </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="19">
+      <c r="A22" s="18">
         <v>5</v>
       </c>
-      <c r="B22" s="18">
-        <f t="shared" si="1"/>
+      <c r="B22" s="17">
+        <f>$A22*B$17</f>
         <v>5</v>
       </c>
-      <c r="C22" s="18">
-        <f t="shared" si="0"/>
+      <c r="C22" s="17">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="D22" s="18">
-        <f t="shared" si="0"/>
+      <c r="D22" s="17">
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="E22" s="18">
-        <f t="shared" si="0"/>
+      <c r="E22" s="17">
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="F22" s="18">
-        <f t="shared" si="0"/>
+      <c r="F22" s="17">
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="13"/>
+      <c r="K22" s="15">
+        <f>SUM(K16:K21)</f>
+        <v>802.8</v>
+      </c>
+      <c r="L22" s="15">
+        <f>SUM(L16:L21)</f>
+        <v>2408.4</v>
+      </c>
+      <c r="M22" s="15">
+        <f>SUM(M16:M21)</f>
+        <v>240.83999999999997</v>
+      </c>
+      <c r="N22" s="15">
+        <f>SUM(N16:N21)</f>
+        <v>3452.04</v>
+      </c>
     </row>
     <row r="23" spans="1:14">
       <c r="B23" t="s">
@@ -1593,10 +1711,10 @@
       <c r="I4" s="4">
         <v>67000</v>
       </c>
-      <c r="L4" s="20" t="s">
+      <c r="L4" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="M4" s="21"/>
+      <c r="M4" s="20"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5">
@@ -1853,10 +1971,10 @@
       <c r="I12" s="4">
         <v>37000</v>
       </c>
-      <c r="L12" s="20" t="s">
+      <c r="L12" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="M12" s="21"/>
+      <c r="M12" s="20"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13">
@@ -2171,10 +2289,10 @@
       <c r="I22" s="4">
         <v>19000</v>
       </c>
-      <c r="L22" s="22" t="s">
+      <c r="L22" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="M22" s="21"/>
+      <c r="M22" s="20"/>
     </row>
     <row r="23" spans="1:16">
       <c r="A23">
